--- a/survey_templates/046_photography_club_theme_voting_form--survey_templates.xlsx
+++ b/survey_templates/046_photography_club_theme_voting_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'theme_1',_'label':_'theme_1'}</t>
+          <t>theme_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'theme_1', 'label': 'Theme 1'}</t>
+          <t>Theme 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'theme_2',_'label':_'theme_2'}</t>
+          <t>theme_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'theme_2', 'label': 'Theme 2'}</t>
+          <t>Theme 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'theme_3',_'label':_'theme_3'}</t>
+          <t>theme_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'theme_3', 'label': 'Theme 3'}</t>
+          <t>Theme 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'theme_4',_'label':_'theme_4'}</t>
+          <t>theme_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'theme_4', 'label': 'Theme 4'}</t>
+          <t>Theme 4</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'theme_5',_'label':_'theme_5'}</t>
+          <t>theme_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'theme_5', 'label': 'Theme 5'}</t>
+          <t>Theme 5</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'theme_6',_'label':_'theme_6'}</t>
+          <t>theme_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'theme_6', 'label': 'Theme 6'}</t>
+          <t>Theme 6</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'theme_7',_'label':_'theme_7'}</t>
+          <t>theme_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'theme_7', 'label': 'Theme 7'}</t>
+          <t>Theme 7</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'theme_8',_'label':_'theme_8'}</t>
+          <t>theme_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'theme_8', 'label': 'Theme 8'}</t>
+          <t>Theme 8</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'theme_9',_'label':_'theme_9'}</t>
+          <t>theme_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'theme_9', 'label': 'Theme 9'}</t>
+          <t>Theme 9</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'theme_10',_'label':_'theme_10'}</t>
+          <t>theme_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'theme_10', 'label': 'Theme 10'}</t>
+          <t>Theme 10</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'theme_11',_'label':_'theme_11'}</t>
+          <t>theme_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'theme_11', 'label': 'Theme 11'}</t>
+          <t>Theme 11</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'theme_12',_'label':_'theme_12'}</t>
+          <t>theme_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'theme_12', 'label': 'Theme 12'}</t>
+          <t>Theme 12</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'member_participation_1',_'label':_'member_participation_1'}</t>
+          <t>member_participation_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'member_participation_1', 'label': 'Member Participation 1'}</t>
+          <t>Member Participation 1</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'member_participation_2',_'label':_'member_participation_2'}</t>
+          <t>member_participation_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'member_participation_2', 'label': 'Member Participation 2'}</t>
+          <t>Member Participation 2</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'member_participation_3',_'label':_'member_participation_3'}</t>
+          <t>member_participation_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'member_participation_3', 'label': 'Member Participation 3'}</t>
+          <t>Member Participation 3</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'theme_13',_'label':_'theme_13'}</t>
+          <t>theme_13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'theme_13', 'label': 'Theme 13'}</t>
+          <t>Theme 13</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'theme_14',_'label':_'theme_14'}</t>
+          <t>theme_14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'theme_14', 'label': 'Theme 14'}</t>
+          <t>Theme 14</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'theme_15',_'label':_'theme_15'}</t>
+          <t>theme_15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'theme_15', 'label': 'Theme 15'}</t>
+          <t>Theme 15</t>
         </is>
       </c>
     </row>
